--- a/output/casestudy_20260807.xlsx
+++ b/output/casestudy_20260807.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>14.29165069999908</v>
+        <v>16.73288849999881</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>14.73938090000047</v>
+        <v>16.89858970000023</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>15.79432869999982</v>
+        <v>17.07389669999975</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>16.13943690000087</v>
+        <v>18.02797540000029</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>16.5443576000016</v>
+        <v>18.8652947999999</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>17.3714129</v>
+        <v>18.19502909999937</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14.3 초</t>
+          <t>16.7 초</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14.7 초</t>
+          <t>16.9 초</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15.8 초</t>
+          <t>17.1 초</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.1 초</t>
+          <t>18.0 초</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16.5 초</t>
+          <t>18.9 초</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17.4 초</t>
+          <t>18.2 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>95.9 초</t>
+          <t>107.0 초</t>
         </is>
       </c>
     </row>
